--- a/Results_experiment/exp_4/summary.xlsx
+++ b/Results_experiment/exp_4/summary.xlsx
@@ -447,13 +447,13 @@
         <v>3055</v>
       </c>
       <c r="D2">
-        <v>0.6863186044526792</v>
+        <v>0.6980251176962882</v>
       </c>
       <c r="E2">
-        <v>3.312101492267063</v>
+        <v>3.249710442505713</v>
       </c>
       <c r="F2">
-        <v>2.17744059805833</v>
+        <v>2.206542165514002</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>3014</v>
       </c>
       <c r="D3">
-        <v>0.5499016252446355</v>
+        <v>0.6532639867745942</v>
       </c>
       <c r="E3">
-        <v>5.232935945228806</v>
+        <v>4.592944229895389</v>
       </c>
       <c r="F3">
-        <v>3.598544122604885</v>
+        <v>3.18430063997088</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>2753</v>
       </c>
       <c r="D4">
-        <v>0.5869961059427942</v>
+        <v>0.5934942333441464</v>
       </c>
       <c r="E4">
-        <v>4.517439197403789</v>
+        <v>4.481760019333977</v>
       </c>
       <c r="F4">
-        <v>3.171088362156588</v>
+        <v>3.128940614538704</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>2231</v>
       </c>
       <c r="D5">
-        <v>0.3467579911947092</v>
+        <v>0.4885972562451482</v>
       </c>
       <c r="E5">
-        <v>2.58697383626416</v>
+        <v>2.288951077679665</v>
       </c>
       <c r="F5">
-        <v>1.647672689984442</v>
+        <v>1.53353938772041</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>1838</v>
       </c>
       <c r="D6">
-        <v>0.3875226487850542</v>
+        <v>0.4265432757453238</v>
       </c>
       <c r="E6">
-        <v>3.661121526063659</v>
+        <v>3.542578258470483</v>
       </c>
       <c r="F6">
-        <v>2.561982172156644</v>
+        <v>2.530136417253348</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>1534</v>
       </c>
       <c r="D7">
-        <v>0.6849446999382298</v>
+        <v>0.7313747557420658</v>
       </c>
       <c r="E7">
-        <v>3.339098134130516</v>
+        <v>3.083253261718648</v>
       </c>
       <c r="F7">
-        <v>2.323001608155449</v>
+        <v>2.158885917514077</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>1348</v>
       </c>
       <c r="D8">
-        <v>0.4228792922279631</v>
+        <v>0.4700802024303762</v>
       </c>
       <c r="E8">
-        <v>2.5535591701753</v>
+        <v>2.44690816010964</v>
       </c>
       <c r="F8">
-        <v>1.856191189863064</v>
+        <v>1.75236778722869</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>572</v>
       </c>
       <c r="D9">
-        <v>0.07912258728554422</v>
+        <v>0.09498909198308858</v>
       </c>
       <c r="E9">
-        <v>6.314288312342598</v>
+        <v>6.259655097297882</v>
       </c>
       <c r="F9">
-        <v>3.996920012261556</v>
+        <v>3.927467536278393</v>
       </c>
     </row>
   </sheetData>
